--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-skindetect.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-skindetect.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>126.8249728679657</v>
+        <v>371.8014767169952</v>
       </c>
       <c r="D2" t="n">
-        <v>6.599999904632568</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1844352847438747</v>
+        <v>0.5208655845287234</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5039370059967041</v>
+        <v>0.5793358087539673</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4350547790527344</v>
+        <v>0.4781144857406616</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4326241016387939</v>
+        <v>0.4699828326702118</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4273204803466797</v>
+        <v>0.4652777910232544</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0923750102519989</v>
+        <v>0.1777942776679992</v>
       </c>
       <c r="K2" t="n">
-        <v>35.16984701156616</v>
+        <v>138.2859280109406</v>
       </c>
       <c r="L2" t="n">
-        <v>0.024588650996142</v>
+        <v>0.06401714948144289</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0479249033597436</v>
+        <v>0.4506076019589263</v>
       </c>
       <c r="N2" t="n">
-        <v>0.049706756478489</v>
+        <v>0.1346391356817566</v>
       </c>
       <c r="O2" t="n">
-        <v>2.483453750610352</v>
+        <v>6.465732097625732</v>
       </c>
       <c r="P2" t="n">
-        <v>4.840415239334106</v>
+        <v>45.51136779785156</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.020382404327393</v>
+        <v>13.59855270385742</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-163759</t>
+          <t>20250725-235030</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>104.8873071670532</v>
+        <v>238.137894153595</v>
       </c>
       <c r="D3" t="n">
-        <v>6.670000076293945</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1885899080240979</v>
+        <v>0.5199863182173835</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5483304262161255</v>
+        <v>0.5031847357749939</v>
       </c>
       <c r="G3" t="n">
-        <v>0.437025785446167</v>
+        <v>0.4398625493049621</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4352000057697296</v>
+        <v>0.4440944790840149</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4342313706874847</v>
+        <v>0.4320785701274872</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09623215347528449</v>
+        <v>0.1789984405040741</v>
       </c>
       <c r="K3" t="n">
-        <v>24.04288077354431</v>
+        <v>134.9323065280914</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0286482725993241</v>
+        <v>0.066563339516668</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0521450609263807</v>
+        <v>0.4333388427696605</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0446552970621845</v>
+        <v>0.1339786572031455</v>
       </c>
       <c r="O3" t="n">
-        <v>2.893475532531738</v>
+        <v>6.722897291183472</v>
       </c>
       <c r="P3" t="n">
-        <v>5.266651153564453</v>
+        <v>43.76722311973572</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.51018500328064</v>
+        <v>13.5318443775177</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-164123</t>
+          <t>20250726-000055</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -841,53 +841,53 @@
         <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>87.7193603515625</v>
+        <v>342.9854383468628</v>
       </c>
       <c r="D4" t="n">
-        <v>6.710000038146973</v>
+        <v>15.55000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1855516873109035</v>
+        <v>0.5243327021598816</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5203883647918701</v>
+        <v>0.5610200166702271</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4454976320266723</v>
+        <v>0.4585987329483032</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4317343235015869</v>
+        <v>0.4590163826942444</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4160583913326263</v>
+        <v>0.4697986543178558</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09550249576568599</v>
+        <v>0.1785968691110611</v>
       </c>
       <c r="K4" t="n">
-        <v>24.1953809261322</v>
+        <v>142.6129357814789</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0277182064434089</v>
+        <v>0.0638659000396728</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0476526364241496</v>
+        <v>0.4368944781841618</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0458435587363668</v>
+        <v>0.1340818239910768</v>
       </c>
       <c r="O4" t="n">
-        <v>2.799538850784302</v>
+        <v>6.450455904006958</v>
       </c>
       <c r="P4" t="n">
-        <v>4.812916278839111</v>
+        <v>44.12634229660034</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.630199432373047</v>
+        <v>13.54226422309876</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-164424</t>
+          <t>20250726-000903</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C5" t="n">
-        <v>61.87150406837464</v>
+        <v>472.8603723049164</v>
       </c>
       <c r="D5" t="n">
-        <v>6.739999771118164</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1840763704644308</v>
+        <v>0.5213820717551492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4795737266540527</v>
+        <v>0.594495415687561</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4020442962646484</v>
+        <v>0.5063291192054749</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4014337062835693</v>
+        <v>0.4930555522441864</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3886925876140594</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.093541644513607</v>
+        <v>0.1783284097909927</v>
       </c>
       <c r="K5" t="n">
-        <v>34.98255705833435</v>
+        <v>160.8411045074463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0285095365920869</v>
+        <v>0.06506737624064531</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0472200200109198</v>
+        <v>0.4468463151761801</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0508301045634959</v>
+        <v>0.1306207628533391</v>
       </c>
       <c r="O5" t="n">
-        <v>2.879463195800781</v>
+        <v>6.571805000305176</v>
       </c>
       <c r="P5" t="n">
-        <v>4.769222021102905</v>
+        <v>45.13147783279419</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.133840560913086</v>
+        <v>13.19269704818726</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-164719</t>
+          <t>20250726-001852</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>77.9796187877655</v>
+        <v>505.4249820709229</v>
       </c>
       <c r="D6" t="n">
-        <v>6.809999942779541</v>
+        <v>15.51000022888184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1848329007625579</v>
+        <v>0.5200160580166315</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4964539110660553</v>
+        <v>0.5553662776947021</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4452296793460846</v>
+        <v>0.4740484356880188</v>
       </c>
       <c r="H6" t="n">
-        <v>0.44601771235466</v>
+        <v>0.4766839444637298</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4366197288036346</v>
+        <v>0.4772727191448211</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09066681563854211</v>
+        <v>0.1780196875333786</v>
       </c>
       <c r="K6" t="n">
-        <v>24.33684778213501</v>
+        <v>152.5851101875305</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0244879935047414</v>
+        <v>0.066477086284373</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0475240036992743</v>
+        <v>0.4336601649180497</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0491792541919368</v>
+        <v>0.1344139457929252</v>
       </c>
       <c r="O6" t="n">
-        <v>2.473287343978882</v>
+        <v>6.71418571472168</v>
       </c>
       <c r="P6" t="n">
-        <v>4.799924373626709</v>
+        <v>43.79967665672302</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.96710467338562</v>
+        <v>13.57580852508545</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-164938</t>
+          <t>20250726-003121</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
-        <v>164.3527629375458</v>
+        <v>359.9291677474976</v>
       </c>
       <c r="D2" t="n">
-        <v>9.75</v>
+        <v>20.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3215254931538193</v>
+        <v>0.595565808541847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5418182015419006</v>
+        <v>0.5363321900367737</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4366412162780761</v>
+        <v>0.4538461565971374</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4280701875686645</v>
+        <v>0.4448160529136657</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4385964870452881</v>
+        <v>0.4545454680919647</v>
       </c>
       <c r="J2" t="n">
-        <v>0.127844825387001</v>
+        <v>0.1391434073448181</v>
       </c>
       <c r="K2" t="n">
-        <v>141.3762745857239</v>
+        <v>204.896333694458</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06373250366437549</v>
+        <v>0.0508203057959528</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4311166352564745</v>
+        <v>0.1605831892183511</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1345199948490256</v>
+        <v>0.1239915602278001</v>
       </c>
       <c r="O2" t="n">
-        <v>6.436982870101929</v>
+        <v>5.132850885391235</v>
       </c>
       <c r="P2" t="n">
-        <v>43.54278016090393</v>
+        <v>16.21890211105347</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.58651947975159</v>
+        <v>12.52314758300781</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-071507</t>
+          <t>20250724-181545</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>615.871363401413</v>
+        <v>374.4404032230377</v>
       </c>
       <c r="D3" t="n">
-        <v>9.930000305175779</v>
+        <v>20.52000045776367</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3226916441850573</v>
+        <v>0.5847411635849211</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5949580073356628</v>
+        <v>0.5457570552825928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5040650367736816</v>
+        <v>0.4341317415237427</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5066224932670593</v>
+        <v>0.4387917220592499</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4943457245826721</v>
+        <v>0.1032863855361938</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1281271874904632</v>
+        <v>0.1404771208763122</v>
       </c>
       <c r="K3" t="n">
-        <v>156.8193368911743</v>
+        <v>204.9979479312897</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0594119529912967</v>
+        <v>0.0563664507157731</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4333504969530766</v>
+        <v>0.1660887109171046</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1329604375480425</v>
+        <v>0.1204776881945015</v>
       </c>
       <c r="O3" t="n">
-        <v>6.000607252120972</v>
+        <v>5.693011522293091</v>
       </c>
       <c r="P3" t="n">
-        <v>43.76840019226074</v>
+        <v>16.77495980262756</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.4290041923523</v>
+        <v>12.16824650764465</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-072207</t>
+          <t>20250724-182650</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>258.8628039360046</v>
+        <v>404.6473019123077</v>
       </c>
       <c r="D4" t="n">
-        <v>9.930000305175779</v>
+        <v>21.04000091552734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3198747406172197</v>
+        <v>0.5868029547365088</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5523809790611267</v>
+        <v>0.551369845867157</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4322470128536224</v>
+        <v>0.4749262630939483</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4308231174945831</v>
+        <v>0.4554140269756317</v>
       </c>
       <c r="I4" t="n">
-        <v>0.454849511384964</v>
+        <v>0.4516128897666931</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1308281272649765</v>
+        <v>0.143003448843956</v>
       </c>
       <c r="K4" t="n">
-        <v>150.880669593811</v>
+        <v>206.221296787262</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0614809659448</v>
+        <v>0.0572051388202327</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4345883921821519</v>
+        <v>0.164427639234184</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1351124815421529</v>
+        <v>0.1206838777749845</v>
       </c>
       <c r="O4" t="n">
-        <v>6.209577560424805</v>
+        <v>5.777719020843506</v>
       </c>
       <c r="P4" t="n">
-        <v>43.89342761039734</v>
+        <v>16.60719156265259</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.64636063575745</v>
+        <v>12.18907165527344</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-073655</t>
+          <t>20250724-183800</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>321.2829329967499</v>
+        <v>410.368488073349</v>
       </c>
       <c r="D5" t="n">
-        <v>9.859999656677246</v>
+        <v>20.30999946594238</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3196383633396842</v>
+        <v>0.5952052550438123</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5561904907226562</v>
+        <v>0.5595855116844177</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4520547986030578</v>
+        <v>0.4991452991962433</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4520547986030578</v>
+        <v>0.5041736364364624</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4478632509708404</v>
+        <v>0.4765217304229736</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1305499374866485</v>
+        <v>0.1394857913255691</v>
       </c>
       <c r="K5" t="n">
-        <v>153.3274481296539</v>
+        <v>205.4439678192139</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0606962147325572</v>
+        <v>0.0531246355264493</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4450639285663567</v>
+        <v>0.1629175762138744</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1340558694140745</v>
+        <v>0.1261718155133842</v>
       </c>
       <c r="O5" t="n">
-        <v>6.130317687988281</v>
+        <v>5.365588188171387</v>
       </c>
       <c r="P5" t="n">
-        <v>44.95145678520203</v>
+        <v>16.45467519760132</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.53964281082153</v>
+        <v>12.74335336685181</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-074540</t>
+          <t>20250724-184941</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
-        <v>163.6600959300995</v>
+        <v>397.9111876487732</v>
       </c>
       <c r="D6" t="n">
-        <v>9.779999732971191</v>
+        <v>22.38999938964844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.317320496947677</v>
+        <v>0.581779028240003</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5467625856399536</v>
+        <v>0.5700325965881348</v>
       </c>
       <c r="G6" t="n">
-        <v>0.483091801404953</v>
+        <v>0.5256609916687012</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4604811072349548</v>
+        <v>0.5159235596656799</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4695945978164673</v>
+        <v>0.5055643916130066</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1284002512693405</v>
+        <v>0.137241393327713</v>
       </c>
       <c r="K6" t="n">
-        <v>152.2715079784393</v>
+        <v>206.7782771587372</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06649318780049231</v>
+        <v>0.051852261666024</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4310484593457515</v>
+        <v>0.1702363089759751</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1368067547826483</v>
+        <v>0.1227603643247396</v>
       </c>
       <c r="O6" t="n">
-        <v>6.715811967849731</v>
+        <v>5.237078428268433</v>
       </c>
       <c r="P6" t="n">
-        <v>43.5358943939209</v>
+        <v>17.19386720657349</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.81748223304748</v>
+        <v>12.39879679679871</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-075520</t>
+          <t>20250724-190138</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>274.9221954345703</v>
+        <v>529.1178040504456</v>
       </c>
       <c r="D2" t="n">
-        <v>14.27000045776367</v>
+        <v>10.78999996185303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5042673239001522</v>
+        <v>0.3303275095655563</v>
       </c>
       <c r="F2" t="n">
-        <v>0.579352855682373</v>
+        <v>0.3636363744735718</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4969135820865631</v>
+        <v>0.3521594703197479</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4917491674423218</v>
+        <v>0.3481228649616241</v>
       </c>
       <c r="I2" t="n">
-        <v>0.476973682641983</v>
+        <v>0.3219814300537109</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1163055375218391</v>
+        <v>0.1562678962945938</v>
       </c>
       <c r="K2" t="n">
-        <v>214.1603753566742</v>
+        <v>81.84259271621704</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0561424529198372</v>
+        <v>0.0588947617181456</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1668170513492999</v>
+        <v>0.1890854363394255</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1207937698553104</v>
+        <v>0.1252271822183439</v>
       </c>
       <c r="O2" t="n">
-        <v>5.670387744903564</v>
+        <v>5.948370933532715</v>
       </c>
       <c r="P2" t="n">
-        <v>16.8485221862793</v>
+        <v>19.09762907028198</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.20017075538635</v>
+        <v>12.64794540405273</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-144818</t>
+          <t>20250727-025953</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
-        <v>264.4513304233551</v>
+        <v>661.5101635456085</v>
       </c>
       <c r="D3" t="n">
-        <v>14.60000038146973</v>
+        <v>10.6899995803833</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4975024736844576</v>
+        <v>0.3330745542871541</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4992199540138244</v>
+        <v>0.5454545617103577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4866561889648437</v>
+        <v>0.4771241843700409</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4905063211917877</v>
+        <v>0.4779050648212433</v>
       </c>
       <c r="I3" t="n">
-        <v>0.46359583735466</v>
+        <v>0.4688524603843689</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1185744851827621</v>
+        <v>0.1585191041231155</v>
       </c>
       <c r="K3" t="n">
-        <v>222.9540982246399</v>
+        <v>99.50737190246582</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0530794965158594</v>
+        <v>0.0596895926069505</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1671046030403364</v>
+        <v>0.1904055859782908</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1201821459401952</v>
+        <v>0.1238635955470623</v>
       </c>
       <c r="O3" t="n">
-        <v>5.361029148101807</v>
+        <v>6.028648853302002</v>
       </c>
       <c r="P3" t="n">
-        <v>16.87756490707397</v>
+        <v>19.23096418380737</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.13839673995972</v>
+        <v>12.5102231502533</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-145809</t>
+          <t>20250727-031144</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>264.0421326160431</v>
+        <v>443.63702750206</v>
       </c>
       <c r="D4" t="n">
-        <v>14.02999973297119</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4957508823046317</v>
+        <v>0.3320781901860848</v>
       </c>
       <c r="F4" t="n">
-        <v>0.53125</v>
+        <v>0.4474123418331146</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4976228177547455</v>
+        <v>0.3860232830047607</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4921630024909973</v>
+        <v>0.3866666555404663</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3726495802402496</v>
+        <v>0.3739837408065796</v>
       </c>
       <c r="J4" t="n">
-        <v>0.118905983865261</v>
+        <v>0.1549287140369415</v>
       </c>
       <c r="K4" t="n">
-        <v>228.6795184612274</v>
+        <v>101.529979467392</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0524718525386092</v>
+        <v>0.0603001164917898</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1672178447836696</v>
+        <v>0.1892475680549546</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1213250018582485</v>
+        <v>0.1241954812909116</v>
       </c>
       <c r="O4" t="n">
-        <v>5.299657106399536</v>
+        <v>6.090311765670776</v>
       </c>
       <c r="P4" t="n">
-        <v>16.88900232315063</v>
+        <v>19.11400437355041</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.2538251876831</v>
+        <v>12.54374361038208</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-150758</t>
+          <t>20250727-032556</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>267.6088197231293</v>
+        <v>386.483172416687</v>
       </c>
       <c r="D5" t="n">
-        <v>13.90999984741211</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="E5" t="n">
-        <v>0.50694707265267</v>
+        <v>0.3312004732363152</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4928909838199615</v>
+        <v>0.4629921317100525</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4776579439640045</v>
+        <v>0.4117647111415863</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4785276055335998</v>
+        <v>0.4109589159488678</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4749999940395355</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="J5" t="n">
-        <v>0.115024983882904</v>
+        <v>0.1522147357463836</v>
       </c>
       <c r="K5" t="n">
-        <v>234.654679775238</v>
+        <v>82.40693712234497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0588953306179235</v>
+        <v>0.0595883213647521</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1611825428386726</v>
+        <v>0.1916226632524245</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1230921273184294</v>
+        <v>0.1239114256188421</v>
       </c>
       <c r="O5" t="n">
-        <v>5.948428392410278</v>
+        <v>6.018420457839966</v>
       </c>
       <c r="P5" t="n">
-        <v>16.27943682670593</v>
+        <v>19.35388898849488</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.43230485916138</v>
+        <v>12.51505398750305</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-151741</t>
+          <t>20250727-033630</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n">
-        <v>314.0055642127991</v>
+        <v>497.2983710765839</v>
       </c>
       <c r="D6" t="n">
-        <v>14.15999984741211</v>
+        <v>10.56999969482422</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4965697564184665</v>
+        <v>0.328464409639669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5631768703460693</v>
+        <v>0.4555984437465668</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4625850319862366</v>
+        <v>0.3385689258575439</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4623287618160248</v>
+        <v>0.3376623392105102</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4543889760971069</v>
+        <v>0.2241992950439453</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1183820962905883</v>
+        <v>0.1855472028255462</v>
       </c>
       <c r="K6" t="n">
-        <v>230.3443839550018</v>
+        <v>94.49049210548399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0565449837410804</v>
+        <v>0.0593119824286734</v>
       </c>
       <c r="M6" t="n">
-        <v>0.162005353682112</v>
+        <v>0.1918003747958948</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1241272605291687</v>
+        <v>0.1253354384167359</v>
       </c>
       <c r="O6" t="n">
-        <v>5.711043357849121</v>
+        <v>5.990510225296021</v>
       </c>
       <c r="P6" t="n">
-        <v>16.36254072189331</v>
+        <v>19.37183785438538</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.53685331344604</v>
+        <v>12.65887928009033</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-152733</t>
+          <t>20250727-034550</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>200.5184094905853</v>
+        <v>286.7677004337311</v>
       </c>
       <c r="D2" t="n">
-        <v>9.619999885559082</v>
+        <v>5.570000171661377</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2914184927940368</v>
+        <v>0.1531759143496552</v>
       </c>
       <c r="F2" t="n">
-        <v>0.375</v>
+        <v>0.5189189314842224</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3215926587581634</v>
+        <v>0.4506172835826874</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3071017265319824</v>
+        <v>0.4307692348957062</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2730769217014313</v>
+        <v>0.4197952151298523</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1231475844979286</v>
+        <v>0.0680062100291252</v>
       </c>
       <c r="K2" t="n">
-        <v>86.96406674385071</v>
+        <v>30.30287861824036</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0549789348451217</v>
+        <v>0.0358185012741844</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1897077654848004</v>
+        <v>0.06486181929559991</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1249996199466214</v>
+        <v>0.0555907003950364</v>
       </c>
       <c r="O2" t="n">
-        <v>5.5528724193573</v>
+        <v>3.617668628692627</v>
       </c>
       <c r="P2" t="n">
-        <v>19.16048431396484</v>
+        <v>6.551043748855591</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.62496161460876</v>
+        <v>5.614660739898682</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-035756</t>
+          <t>20250728-062105</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>207.46892786026</v>
+        <v>428.2584402561188</v>
       </c>
       <c r="D3" t="n">
-        <v>9.489999771118164</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="E3" t="n">
-        <v>0.294188208050198</v>
+        <v>0.1531152980955871</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3456375896930694</v>
+        <v>0.5380710363388062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3225806355476379</v>
+        <v>0.4386503100395202</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3079584836959839</v>
+        <v>0.4376996755599975</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3102310299873352</v>
+        <v>0.4330275356769562</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1228775903582573</v>
+        <v>0.0654416382312774</v>
       </c>
       <c r="K3" t="n">
-        <v>96.04823398590088</v>
+        <v>29.87554979324341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0601278956573788</v>
+        <v>0.0341317252357407</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1897009858990659</v>
+        <v>0.061857268361762</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1246811328548015</v>
+        <v>0.0559910264345678</v>
       </c>
       <c r="O3" t="n">
-        <v>6.072917461395264</v>
+        <v>3.447304248809814</v>
       </c>
       <c r="P3" t="n">
-        <v>19.15979957580566</v>
+        <v>6.247584104537964</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.59279441833496</v>
+        <v>5.655093669891357</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-040424</t>
+          <t>20250728-062723</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>203.8756771087646</v>
+        <v>267.2858548164368</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>5.650000095367432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2951887481742435</v>
+        <v>0.1527906999639842</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3978102207183838</v>
+        <v>0.541218638420105</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3658536672592163</v>
+        <v>0.4362017810344696</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3685092031955719</v>
+        <v>0.4298093616962433</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2820512950420379</v>
+        <v>0.4293193817138672</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1204068884253501</v>
+        <v>0.0669032260775566</v>
       </c>
       <c r="K4" t="n">
-        <v>94.01212167739868</v>
+        <v>40.36270809173584</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0567226834816507</v>
+        <v>0.0379439674981749</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1896843768582485</v>
+        <v>0.0614262500611862</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1231732250440238</v>
+        <v>0.0557693538099232</v>
       </c>
       <c r="O4" t="n">
-        <v>5.728991031646729</v>
+        <v>3.832340717315674</v>
       </c>
       <c r="P4" t="n">
-        <v>19.15812206268311</v>
+        <v>6.20405125617981</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.44049572944641</v>
+        <v>5.632704734802246</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-041109</t>
+          <t>20250728-063550</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>208.4999167919159</v>
+        <v>266.9950461387634</v>
       </c>
       <c r="D5" t="n">
-        <v>9.720000267028809</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2980603592263328</v>
+        <v>0.1534033310802086</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4052287638187408</v>
+        <v>0.4539249241352081</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3257443010807037</v>
+        <v>0.395348846912384</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3240418136119842</v>
+        <v>0.3933333456516266</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3056768476963043</v>
+        <v>0.3682539761066437</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209064051508903</v>
+        <v>0.0637309774756431</v>
       </c>
       <c r="K5" t="n">
-        <v>93.54327797889709</v>
+        <v>32.04149675369263</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0558423169768682</v>
+        <v>0.0334353848259047</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1890671158781146</v>
+        <v>0.0581994717664057</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1239818488017167</v>
+        <v>0.059374462259878</v>
       </c>
       <c r="O5" t="n">
-        <v>5.640074014663696</v>
+        <v>3.376973867416382</v>
       </c>
       <c r="P5" t="n">
-        <v>19.09577870368957</v>
+        <v>5.878146648406982</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.52216672897339</v>
+        <v>5.996820688247681</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-041747</t>
+          <t>20250728-064157</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>205.4355897903442</v>
+        <v>356.7854146957397</v>
       </c>
       <c r="D6" t="n">
-        <v>9.350000381469728</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2974002179172303</v>
+        <v>0.1528172434353437</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3705036044120788</v>
+        <v>0.5249537825584412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3245749473571777</v>
+        <v>0.4716981053352356</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3189368844032287</v>
+        <v>0.4671052694320678</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3149350583553314</v>
+        <v>0.4569536447525024</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1198602840304374</v>
+        <v>0.06624790281057349</v>
       </c>
       <c r="K6" t="n">
-        <v>93.33917903900146</v>
+        <v>34.53935766220093</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0582258134785265</v>
+        <v>0.0348585879448616</v>
       </c>
       <c r="M6" t="n">
-        <v>0.192545218042808</v>
+        <v>0.0581867411585137</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1242810664790691</v>
+        <v>0.0564241055214759</v>
       </c>
       <c r="O6" t="n">
-        <v>5.880807161331177</v>
+        <v>3.52071738243103</v>
       </c>
       <c r="P6" t="n">
-        <v>19.44706702232361</v>
+        <v>5.876860857009888</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.55238771438599</v>
+        <v>5.698834657669067</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-042430</t>
+          <t>20250728-064755</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C2" t="n">
-        <v>111.1117160320282</v>
+        <v>341.8987267017365</v>
       </c>
       <c r="D2" t="n">
-        <v>3.200000047683716</v>
+        <v>7.429999828338623</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1554847293429904</v>
+        <v>0.254373550778482</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3522727191448211</v>
+        <v>0.5308848023414612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2935251891613006</v>
+        <v>0.4725457429885864</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2969697117805481</v>
+        <v>0.4715718924999237</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3140740692615509</v>
+        <v>0.4664310812950134</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0598715431988239</v>
+        <v>0.1037105619907379</v>
       </c>
       <c r="K2" t="n">
-        <v>29.90208101272583</v>
+        <v>56.3090455532074</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0336167198596614</v>
+        <v>0.0449397894415524</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0646825450481754</v>
+        <v>0.1105606178245922</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0601747909394821</v>
+        <v>0.0936669689593928</v>
       </c>
       <c r="O2" t="n">
-        <v>3.395288705825806</v>
+        <v>4.538918733596802</v>
       </c>
       <c r="P2" t="n">
-        <v>6.532937049865723</v>
+        <v>11.16662240028381</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.077653884887695</v>
+        <v>9.460363864898682</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-180719</t>
+          <t>20250729-100140</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
-        <v>117.9024384021759</v>
+        <v>348.3476157188416</v>
       </c>
       <c r="D3" t="n">
-        <v>3.299999952316284</v>
+        <v>7.53000020980835</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1545815263923845</v>
+        <v>0.2524460738613492</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3859060406684875</v>
+        <v>0.4801324605941772</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3313953578472137</v>
+        <v>0.4386252164840698</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3338533639907837</v>
+        <v>0.4386252164840698</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3397913575172424</v>
+        <v>0.424722671508789</v>
       </c>
       <c r="J3" t="n">
-        <v>0.059523057192564</v>
+        <v>0.1015101671218872</v>
       </c>
       <c r="K3" t="n">
-        <v>32.19410729408264</v>
+        <v>65.1654360294342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0397914234954531</v>
+        <v>0.042465068326138</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0638632443871828</v>
+        <v>0.1146931199744196</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0559897918512325</v>
+        <v>0.09185571009569821</v>
       </c>
       <c r="O3" t="n">
-        <v>4.018933773040772</v>
+        <v>4.288971900939941</v>
       </c>
       <c r="P3" t="n">
-        <v>6.450187683105469</v>
+        <v>11.58400511741638</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.654968976974487</v>
+        <v>9.277426719665527</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-181030</t>
+          <t>20250729-100947</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C4" t="n">
-        <v>112.5206217765808</v>
+        <v>427.3287937641144</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>7.980000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1577397767040464</v>
+        <v>0.2518986867597469</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3654159903526306</v>
+        <v>0.5591397881507874</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3410013616085052</v>
+        <v>0.4910179674625397</v>
       </c>
       <c r="H4" t="n">
-        <v>0.340624988079071</v>
+        <v>0.48407644033432</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2267657965421676</v>
+        <v>0.4776119291782379</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0598972700536251</v>
+        <v>0.1028980016708374</v>
       </c>
       <c r="K4" t="n">
-        <v>41.06228804588318</v>
+        <v>66.63164567947388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0354051306696221</v>
+        <v>0.0420307546558946</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0587337796050723</v>
+        <v>0.1122158824807346</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0574000660735781</v>
+        <v>0.0964348268981027</v>
       </c>
       <c r="O4" t="n">
-        <v>3.575918197631836</v>
+        <v>4.245106220245361</v>
       </c>
       <c r="P4" t="n">
-        <v>5.932111740112305</v>
+        <v>11.3338041305542</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.797406673431396</v>
+        <v>9.739917516708374</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-181401</t>
+          <t>20250729-101758</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>109.663028717041</v>
+        <v>204.3394632339477</v>
       </c>
       <c r="D5" t="n">
-        <v>3.319999933242798</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1557100903656747</v>
+        <v>0.2552405347426732</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3476923108100891</v>
+        <v>0.3727598488330841</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3316326439380646</v>
+        <v>0.3180328011512756</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3305785059928894</v>
+        <v>0.3084745705127716</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3256579041481018</v>
+        <v>0.3190789520740509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06565599888563151</v>
+        <v>0.1015709415078163</v>
       </c>
       <c r="K5" t="n">
-        <v>35.03859901428223</v>
+        <v>67.18026852607727</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0359205656712598</v>
+        <v>0.0458137115629592</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0637627875450814</v>
+        <v>0.1110885190491629</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0558642986977454</v>
+        <v>0.09725205733044311</v>
       </c>
       <c r="O5" t="n">
-        <v>3.627977132797241</v>
+        <v>4.627184867858887</v>
       </c>
       <c r="P5" t="n">
-        <v>6.440041542053223</v>
+        <v>11.21994042396545</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.64229416847229</v>
+        <v>9.822457790374756</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-181723</t>
+          <t>20250729-102719</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
-        <v>113.3723571300507</v>
+        <v>381.8870842456818</v>
       </c>
       <c r="D6" t="n">
-        <v>3.180000066757202</v>
+        <v>7.730000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1557970783776706</v>
+        <v>0.2539554490991261</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3467094600200653</v>
+        <v>0.5214521288871765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3058186769485473</v>
+        <v>0.4213938415050506</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2902208268642425</v>
+        <v>0.4213938415050506</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2916052937507629</v>
+        <v>0.4112769365310669</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0588044747710228</v>
+        <v>0.1362645924091339</v>
       </c>
       <c r="K6" t="n">
-        <v>32.89898777008057</v>
+        <v>59.91131949424744</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0365948771486187</v>
+        <v>0.0460806907993732</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0587662635463299</v>
+        <v>0.11407203957586</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0602195333726335</v>
+        <v>0.0972604916827513</v>
       </c>
       <c r="O6" t="n">
-        <v>3.696082592010498</v>
+        <v>4.654149770736694</v>
       </c>
       <c r="P6" t="n">
-        <v>5.935392618179321</v>
+        <v>11.52127599716186</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.082172870635986</v>
+        <v>9.823309659957886</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-182049</t>
+          <t>20250729-103258</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>160.5383262634277</v>
+        <v>198.7794506549835</v>
       </c>
       <c r="D2" t="n">
-        <v>6.630000114440918</v>
+        <v>10.82999992370606</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2482722890045907</v>
+        <v>0.1740194124051894</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4658493995666504</v>
+        <v>0.2973451316356659</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3968504071235657</v>
+        <v>0.2774957716464996</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3893510699272156</v>
+        <v>0.2767075300216675</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3294509053230285</v>
+        <v>0.2841918170452118</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0911397486925125</v>
+        <v>0.0875102579593658</v>
       </c>
       <c r="K2" t="n">
-        <v>54.9705536365509</v>
+        <v>27.28475427627563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0498348934815661</v>
+        <v>0.0288639823989112</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1152061519056263</v>
+        <v>0.0333722204265027</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09287274710022569</v>
+        <v>0.0241320652536826</v>
       </c>
       <c r="O2" t="n">
-        <v>5.033324241638184</v>
+        <v>2.915262222290039</v>
       </c>
       <c r="P2" t="n">
-        <v>11.63582134246826</v>
+        <v>3.370594263076782</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.380147457122805</v>
+        <v>2.437338590621948</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-062943</t>
+          <t>20250730-094624</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="C3" t="n">
-        <v>163.6030504703522</v>
+        <v>229.268161535263</v>
       </c>
       <c r="D3" t="n">
-        <v>6.800000190734863</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2480315061079131</v>
+        <v>0.1742965813839073</v>
       </c>
       <c r="F3" t="n">
-        <v>0.393194705247879</v>
+        <v>0.3171247243881225</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3265940845012665</v>
+        <v>0.3014705777168274</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3235294222831726</v>
+        <v>0.2953270971775055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3349436521530151</v>
+        <v>0.2981131970882416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0918995440006256</v>
+        <v>0.0876318737864494</v>
       </c>
       <c r="K3" t="n">
-        <v>82.07996964454651</v>
+        <v>27.5026638507843</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0496297189504793</v>
+        <v>0.0303382141755359</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1122546148772287</v>
+        <v>0.0333109374093537</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0993323703803638</v>
+        <v>0.0247012223347578</v>
       </c>
       <c r="O3" t="n">
-        <v>5.012601613998413</v>
+        <v>3.064159631729126</v>
       </c>
       <c r="P3" t="n">
-        <v>11.3377161026001</v>
+        <v>3.364404678344727</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.03256940841675</v>
+        <v>2.494823455810547</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-063439</t>
+          <t>20250730-095053</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C4" t="n">
-        <v>161.0309021472931</v>
+        <v>250.447249174118</v>
       </c>
       <c r="D4" t="n">
-        <v>7.150000095367432</v>
+        <v>10.72999954223633</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2429594579670163</v>
+        <v>0.174991066350001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3779264092445373</v>
+        <v>0.2532750964164734</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3732394278049469</v>
+        <v>0.2580645084381103</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3731884062290191</v>
+        <v>0.2580645084381103</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3624382317066192</v>
+        <v>0.253699779510498</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1008748188614845</v>
+        <v>0.1039872914552688</v>
       </c>
       <c r="K4" t="n">
-        <v>56.17799115180969</v>
+        <v>17.05436110496521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0500074542394959</v>
+        <v>0.0391751563194954</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1134726411045187</v>
+        <v>0.0372784161331629</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1002809316805093</v>
+        <v>0.0241423786276637</v>
       </c>
       <c r="O4" t="n">
-        <v>5.050752878189087</v>
+        <v>3.956690788269043</v>
       </c>
       <c r="P4" t="n">
-        <v>11.4607367515564</v>
+        <v>3.765120029449463</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.12837409973144</v>
+        <v>2.438380241394043</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-063955</t>
+          <t>20250730-095553</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>158.985999584198</v>
+        <v>189.1704258918762</v>
       </c>
       <c r="D5" t="n">
-        <v>6.900000095367432</v>
+        <v>10.63000011444092</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2498492217726177</v>
+        <v>0.1752926358975559</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4171539843082428</v>
+        <v>0.2484848499298095</v>
       </c>
       <c r="G5" t="n">
-        <v>0.354463130235672</v>
+        <v>0.2622950673103332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3384094834327698</v>
+        <v>0.2586520910263061</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3509933650493622</v>
+        <v>0.2554744482040405</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1209640726447105</v>
+        <v>0.1000420525670051</v>
       </c>
       <c r="K5" t="n">
-        <v>59.99718737602234</v>
+        <v>27.50289368629456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0489524638298714</v>
+        <v>0.0299857040443042</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1171716746717396</v>
+        <v>0.0333742528858751</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0916611628957314</v>
+        <v>0.0247461748595284</v>
       </c>
       <c r="O5" t="n">
-        <v>4.944198846817017</v>
+        <v>3.028556108474731</v>
       </c>
       <c r="P5" t="n">
-        <v>11.8343391418457</v>
+        <v>3.370799541473389</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.257777452468872</v>
+        <v>2.499363660812378</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-064453</t>
+          <t>20250730-100105</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>164.1821789741516</v>
+        <v>247.5253162384033</v>
       </c>
       <c r="D6" t="n">
-        <v>6.630000114440918</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2470538384384578</v>
+        <v>0.1763636436417838</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4067278206348419</v>
+        <v>0.2875536382198334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3799705505371094</v>
+        <v>0.2862823009490967</v>
       </c>
       <c r="H6" t="n">
-        <v>0.377880185842514</v>
+        <v>0.2862823009490967</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3757961690425873</v>
+        <v>0.2926829159259796</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0942158997058868</v>
+        <v>0.0881734490394592</v>
       </c>
       <c r="K6" t="n">
-        <v>72.73522210121155</v>
+        <v>16.72739124298096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0466022515060878</v>
+        <v>0.0306341931371405</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1116170812361311</v>
+        <v>0.0371547925590288</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1011242323582715</v>
+        <v>0.0248599807814796</v>
       </c>
       <c r="O6" t="n">
-        <v>4.706827402114868</v>
+        <v>3.094053506851196</v>
       </c>
       <c r="P6" t="n">
-        <v>11.27332520484924</v>
+        <v>3.752634048461914</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.21354746818542</v>
+        <v>2.510858058929444</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-064952</t>
+          <t>20250730-100525</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>238.802325963974</v>
+        <v>255.6579349040985</v>
       </c>
       <c r="D2" t="n">
-        <v>1.840000033378601</v>
+        <v>13.73999977111816</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1334321940842183</v>
+        <v>0.2802561627722335</v>
       </c>
       <c r="F2" t="n">
-        <v>0.499009907245636</v>
+        <v>0.5525846481323242</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4293380975723266</v>
+        <v>0.4891846776008606</v>
       </c>
       <c r="H2" t="n">
-        <v>0.414179116487503</v>
+        <v>0.4858568906784057</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4067164063453674</v>
+        <v>0.477031797170639</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1202978938817977</v>
+        <v>0.0913210213184356</v>
       </c>
       <c r="K2" t="n">
-        <v>25.0634286403656</v>
+        <v>48.97410774230957</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0397333225401321</v>
+        <v>0.0270750617036725</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0280961447423047</v>
+        <v>0.1065303217066396</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0370911890917485</v>
+        <v>0.0581333566420149</v>
       </c>
       <c r="O2" t="n">
-        <v>4.013065576553345</v>
+        <v>2.734581232070923</v>
       </c>
       <c r="P2" t="n">
-        <v>2.837710618972778</v>
+        <v>10.7595624923706</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.746210098266602</v>
+        <v>5.871469020843506</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-192155</t>
+          <t>20250731-023719</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n">
-        <v>167.8125958442688</v>
+        <v>243.2809979915619</v>
       </c>
       <c r="D3" t="n">
-        <v>1.820000052452088</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1334946422089992</v>
+        <v>0.279700188033552</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4918625652790069</v>
+        <v>0.5428571701049805</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4242424368858337</v>
+        <v>0.475862056016922</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4257602989673614</v>
+        <v>0.4658493995666504</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4149659872055053</v>
+        <v>0.4535714387893677</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1229549273848533</v>
+        <v>0.0900050327181816</v>
       </c>
       <c r="K3" t="n">
-        <v>13.90723872184753</v>
+        <v>48.4695258140564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0437456876924722</v>
+        <v>0.0274119636800029</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0328570309251841</v>
+        <v>0.1064952529302918</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0332127844933236</v>
+        <v>0.0579121112823486</v>
       </c>
       <c r="O3" t="n">
-        <v>4.418314456939697</v>
+        <v>2.768608331680298</v>
       </c>
       <c r="P3" t="n">
-        <v>3.318560123443604</v>
+        <v>10.75602054595947</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.354491233825684</v>
+        <v>5.849123239517212</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-192706</t>
+          <t>20250731-024325</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>268.0829870700836</v>
+        <v>243.1020905971527</v>
       </c>
       <c r="D4" t="n">
-        <v>1.850000023841858</v>
+        <v>13.77999973297119</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1338379158273986</v>
+        <v>0.2801612310380821</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5132075548171997</v>
+        <v>0.5364120602607727</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4566666781902313</v>
+        <v>0.4677419364452362</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4419889450073242</v>
+        <v>0.4628378450870514</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4684385359287262</v>
+        <v>0.467576801776886</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1240463480353355</v>
+        <v>0.0931156054139137</v>
       </c>
       <c r="K4" t="n">
-        <v>24.50869822502136</v>
+        <v>49.21252608299256</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0401643219560679</v>
+        <v>0.0275860399302869</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0284928567338698</v>
+        <v>0.1053651630288303</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03296692064493</v>
+        <v>0.0583537757986843</v>
       </c>
       <c r="O4" t="n">
-        <v>4.056596517562866</v>
+        <v>2.786190032958984</v>
       </c>
       <c r="P4" t="n">
-        <v>2.87777853012085</v>
+        <v>10.64188146591186</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.329658985137939</v>
+        <v>5.893731355667114</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-193054</t>
+          <t>20250731-024919</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>149.5940852165222</v>
+        <v>197.2125747203827</v>
       </c>
       <c r="D5" t="n">
-        <v>1.840000033378601</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1363012978718394</v>
+        <v>0.2804574481586911</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4950166046619415</v>
+        <v>0.5281553268432617</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3754045367240906</v>
+        <v>0.4651952385902405</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3683241307735443</v>
+        <v>0.4456521868705749</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3767605721950531</v>
+        <v>0.4448529481887817</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1181853637099266</v>
+        <v>0.094117134809494</v>
       </c>
       <c r="K5" t="n">
-        <v>24.45796012878418</v>
+        <v>49.01338005065918</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0430511956167693</v>
+        <v>0.0303836128499248</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0315057641208762</v>
+        <v>0.1069393748103982</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0334881555916059</v>
+        <v>0.0628777423707565</v>
       </c>
       <c r="O5" t="n">
-        <v>4.348170757293701</v>
+        <v>3.068744897842407</v>
       </c>
       <c r="P5" t="n">
-        <v>3.182082176208496</v>
+        <v>10.80087685585022</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.382303714752197</v>
+        <v>6.350651979446411</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-193633</t>
+          <t>20250731-025514</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>167.5420274734497</v>
+        <v>278.6678340435028</v>
       </c>
       <c r="D6" t="n">
-        <v>1.850000023841858</v>
+        <v>13.76000022888184</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1355126920930096</v>
+        <v>0.2804834657593777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5038167834281921</v>
+        <v>0.5586591958999634</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4271186292171478</v>
+        <v>0.4734133780002594</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4194107353687286</v>
+        <v>0.4726631343364715</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4224872291088104</v>
+        <v>0.4730434715747833</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1248232424259185</v>
+        <v>0.0891655758023262</v>
       </c>
       <c r="K6" t="n">
-        <v>24.37797141075134</v>
+        <v>49.49047660827637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0438939816880934</v>
+        <v>0.0291794054579026</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0282688424138739</v>
+        <v>0.1081609371865149</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0337517049052927</v>
+        <v>0.0625288226816913</v>
       </c>
       <c r="O6" t="n">
-        <v>4.433292150497437</v>
+        <v>2.947119951248169</v>
       </c>
       <c r="P6" t="n">
-        <v>2.855153083801269</v>
+        <v>10.92425465583801</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.40892219543457</v>
+        <v>6.31541109085083</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-194014</t>
+          <t>20250731-030012</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>222.1773517131805</v>
+        <v>126.8249728679657</v>
       </c>
       <c r="D2" t="n">
-        <v>5.760000228881836</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1404397626903569</v>
+        <v>0.1844352847438747</v>
       </c>
       <c r="F2" t="n">
-        <v>0.268398255109787</v>
+        <v>0.5039370059967041</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2625482678413391</v>
+        <v>0.4350547790527344</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2575452625751495</v>
+        <v>0.4326241016387939</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2596348822116852</v>
+        <v>0.4273204803466797</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0885892435908317</v>
+        <v>0.0923750102519989</v>
       </c>
       <c r="K2" t="n">
-        <v>27.43926930427552</v>
+        <v>35.16984701156616</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0348292553778922</v>
+        <v>0.024588650996142</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0371806125829715</v>
+        <v>0.0479249033597436</v>
       </c>
       <c r="N2" t="n">
-        <v>0.024876596904037</v>
+        <v>0.049706756478489</v>
       </c>
       <c r="O2" t="n">
-        <v>3.517754793167114</v>
+        <v>2.483453750610352</v>
       </c>
       <c r="P2" t="n">
-        <v>3.755241870880127</v>
+        <v>4.840415239334106</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.51253628730774</v>
+        <v>5.020382404327393</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-091029</t>
+          <t>20250627-163759</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>151.4773399829865</v>
+        <v>104.8873071670532</v>
       </c>
       <c r="D3" t="n">
-        <v>5.860000133514404</v>
+        <v>6.670000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1404025657495982</v>
+        <v>0.1885899080240979</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2585034072399139</v>
+        <v>0.5483304262161255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2242990583181381</v>
+        <v>0.437025785446167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2181069999933242</v>
+        <v>0.4352000057697296</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2063157856464386</v>
+        <v>0.4342313706874847</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1000477895140647</v>
+        <v>0.09623215347528449</v>
       </c>
       <c r="K3" t="n">
-        <v>27.58947277069092</v>
+        <v>24.04288077354431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0339655876159668</v>
+        <v>0.0286482725993241</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0331537227819461</v>
+        <v>0.0521450609263807</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0253044968784445</v>
+        <v>0.0446552970621845</v>
       </c>
       <c r="O3" t="n">
-        <v>3.430524349212646</v>
+        <v>2.893475532531738</v>
       </c>
       <c r="P3" t="n">
-        <v>3.348526000976562</v>
+        <v>5.266651153564453</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5557541847229</v>
+        <v>4.51018500328064</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-091523</t>
+          <t>20250627-164123</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>225.3855805397034</v>
+        <v>87.7193603515625</v>
       </c>
       <c r="D4" t="n">
-        <v>5.739999771118164</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1427183900481072</v>
+        <v>0.1855516873109035</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3201376795768738</v>
+        <v>0.5203883647918701</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2668863236904144</v>
+        <v>0.4454976320266723</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2668863236904144</v>
+        <v>0.4317343235015869</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2664298415184021</v>
+        <v>0.4160583913326263</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0856814607977867</v>
+        <v>0.09550249576568599</v>
       </c>
       <c r="K4" t="n">
-        <v>17.21365904808044</v>
+        <v>24.1953809261322</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0353503014781687</v>
+        <v>0.0277182064434089</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0338377197190086</v>
+        <v>0.0476526364241496</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0311513584439117</v>
+        <v>0.0458435587363668</v>
       </c>
       <c r="O4" t="n">
-        <v>3.570380449295044</v>
+        <v>2.799538850784302</v>
       </c>
       <c r="P4" t="n">
-        <v>3.417609691619873</v>
+        <v>4.812916278839111</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.146287202835083</v>
+        <v>4.630199432373047</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-091906</t>
+          <t>20250627-164424</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>206.3349559307098</v>
+        <v>61.87150406837464</v>
       </c>
       <c r="D5" t="n">
-        <v>5.769999980926514</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1412675570357929</v>
+        <v>0.1840763704644308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2620967626571655</v>
+        <v>0.4795737266540527</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2527472674846649</v>
+        <v>0.4020442962646484</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2485659718513488</v>
+        <v>0.4014337062835693</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2357563823461532</v>
+        <v>0.3886925876140594</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0915681794285774</v>
+        <v>0.093541644513607</v>
       </c>
       <c r="K5" t="n">
-        <v>28.07018852233887</v>
+        <v>34.98255705833435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03184706385773</v>
+        <v>0.0285095365920869</v>
       </c>
       <c r="M5" t="n">
-        <v>0.033892537107562</v>
+        <v>0.0472200200109198</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0250800836204302</v>
+        <v>0.0508301045634959</v>
       </c>
       <c r="O5" t="n">
-        <v>3.216553449630737</v>
+        <v>2.879463195800781</v>
       </c>
       <c r="P5" t="n">
-        <v>3.423146247863769</v>
+        <v>4.769222021102905</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.533088445663452</v>
+        <v>5.133840560913086</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-092354</t>
+          <t>20250627-164719</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>174.0874073505402</v>
+        <v>77.9796187877655</v>
       </c>
       <c r="D6" t="n">
-        <v>5.659999847412109</v>
+        <v>6.809999942779541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1418429769306297</v>
+        <v>0.1848329007625579</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2751938104629516</v>
+        <v>0.4964539110660553</v>
       </c>
       <c r="G6" t="n">
-        <v>0.270676702260971</v>
+        <v>0.4452296793460846</v>
       </c>
       <c r="H6" t="n">
-        <v>0.270676702260971</v>
+        <v>0.44601771235466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2739211916923523</v>
+        <v>0.4366197288036346</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0855400040745735</v>
+        <v>0.09066681563854211</v>
       </c>
       <c r="K6" t="n">
-        <v>27.39664530754089</v>
+        <v>24.33684778213501</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0319882997191778</v>
+        <v>0.0244879935047414</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0336341598246357</v>
+        <v>0.0475240036992743</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0251332792905297</v>
+        <v>0.0491792541919368</v>
       </c>
       <c r="O6" t="n">
-        <v>3.230818271636963</v>
+        <v>2.473287343978882</v>
       </c>
       <c r="P6" t="n">
-        <v>3.397050142288208</v>
+        <v>4.799924373626709</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.538461208343506</v>
+        <v>4.96710467338562</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-092832</t>
+          <t>20250627-164938</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C2" t="n">
-        <v>213.3456435203552</v>
+        <v>238.802325963974</v>
       </c>
       <c r="D2" t="n">
-        <v>7.550000190734863</v>
+        <v>1.840000033378601</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1912315522248928</v>
+        <v>0.1334321940842183</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5653846263885498</v>
+        <v>0.499009907245636</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4939965605735779</v>
+        <v>0.4293380975723266</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4869565069675445</v>
+        <v>0.414179116487503</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4814159274101257</v>
+        <v>0.4067164063453674</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07410790771245949</v>
+        <v>0.1202978938817977</v>
       </c>
       <c r="K2" t="n">
-        <v>37.99041700363159</v>
+        <v>25.0634286403656</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0374717381921145</v>
+        <v>0.0397333225401321</v>
       </c>
       <c r="M2" t="n">
-        <v>0.110409396709782</v>
+        <v>0.0280961447423047</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0642140973912607</v>
+        <v>0.0370911890917485</v>
       </c>
       <c r="O2" t="n">
-        <v>3.784645557403565</v>
+        <v>4.013065576553345</v>
       </c>
       <c r="P2" t="n">
-        <v>11.15134906768799</v>
+        <v>2.837710618972778</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.485623836517334</v>
+        <v>3.746210098266602</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-111336</t>
+          <t>20250701-192155</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>152.2499334812164</v>
+        <v>167.8125958442688</v>
       </c>
       <c r="D3" t="n">
-        <v>7.550000190734863</v>
+        <v>1.820000052452088</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1921913564678222</v>
+        <v>0.1334946422089992</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5398550629615784</v>
+        <v>0.4918625652790069</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4832214713096618</v>
+        <v>0.4242424368858337</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4832214713096618</v>
+        <v>0.4257602989673614</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4863945543766022</v>
+        <v>0.4149659872055053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07198351621627801</v>
+        <v>0.1229549273848533</v>
       </c>
       <c r="K3" t="n">
-        <v>49.22374081611633</v>
+        <v>13.90723872184753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0336370798620847</v>
+        <v>0.0437456876924722</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1060786884610015</v>
+        <v>0.0328570309251841</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0573925358234065</v>
+        <v>0.0332127844933236</v>
       </c>
       <c r="O3" t="n">
-        <v>3.397345066070557</v>
+        <v>4.418314456939697</v>
       </c>
       <c r="P3" t="n">
-        <v>10.71394753456116</v>
+        <v>3.318560123443604</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.796646118164063</v>
+        <v>3.354491233825684</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-111842</t>
+          <t>20250701-192706</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>168.7208433151245</v>
+        <v>268.0829870700836</v>
       </c>
       <c r="D4" t="n">
-        <v>7.860000133514404</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1907841930506934</v>
+        <v>0.1338379158273986</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5404411554336548</v>
+        <v>0.5132075548171997</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4612676203250885</v>
+        <v>0.4566666781902313</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4555160105228424</v>
+        <v>0.4419889450073242</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4424131512641907</v>
+        <v>0.4684385359287262</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07230339199304581</v>
+        <v>0.1240463480353355</v>
       </c>
       <c r="K4" t="n">
-        <v>50.05670213699341</v>
+        <v>24.50869822502136</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0322674548271859</v>
+        <v>0.0401643219560679</v>
       </c>
       <c r="M4" t="n">
-        <v>0.104231060141384</v>
+        <v>0.0284928567338698</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0574715609597687</v>
+        <v>0.03296692064493</v>
       </c>
       <c r="O4" t="n">
-        <v>3.259012937545776</v>
+        <v>4.056596517562866</v>
       </c>
       <c r="P4" t="n">
-        <v>10.52733707427978</v>
+        <v>2.87777853012085</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.804627656936646</v>
+        <v>3.329658985137939</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-112308</t>
+          <t>20250701-193054</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="C5" t="n">
-        <v>204.8322422504425</v>
+        <v>149.5940852165222</v>
       </c>
       <c r="D5" t="n">
-        <v>7.570000171661377</v>
+        <v>1.840000033378601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1910979401791232</v>
+        <v>0.1363012978718394</v>
       </c>
       <c r="F5" t="n">
-        <v>0.542553186416626</v>
+        <v>0.4950166046619415</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4599303007125854</v>
+        <v>0.3754045367240906</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4599303007125854</v>
+        <v>0.3683241307735443</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4602076113224029</v>
+        <v>0.3767605721950531</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07220945507287969</v>
+        <v>0.1181853637099266</v>
       </c>
       <c r="K5" t="n">
-        <v>38.85470509529114</v>
+        <v>24.45796012878418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0329312924111243</v>
+        <v>0.0430511956167693</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1041435605228537</v>
+        <v>0.0315057641208762</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0583786020184507</v>
+        <v>0.0334881555916059</v>
       </c>
       <c r="O5" t="n">
-        <v>3.32606053352356</v>
+        <v>4.348170757293701</v>
       </c>
       <c r="P5" t="n">
-        <v>10.51849961280823</v>
+        <v>3.182082176208496</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.896238803863525</v>
+        <v>3.382303714752197</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-112750</t>
+          <t>20250701-193633</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>197.5474433898925</v>
+        <v>167.5420274734497</v>
       </c>
       <c r="D6" t="n">
-        <v>7.460000038146973</v>
+        <v>1.850000023841858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1916242076689938</v>
+        <v>0.1355126920930096</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5553538799285889</v>
+        <v>0.5038167834281921</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4628670215606689</v>
+        <v>0.4271186292171478</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4307115972042084</v>
+        <v>0.4194107353687286</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3992395401000976</v>
+        <v>0.4224872291088104</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0727434605360031</v>
+        <v>0.1248232424259185</v>
       </c>
       <c r="K6" t="n">
-        <v>38.35925078392029</v>
+        <v>24.37797141075134</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0325917937968036</v>
+        <v>0.0438939816880934</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1037084135678735</v>
+        <v>0.0282688424138739</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0579455347344426</v>
+        <v>0.0337517049052927</v>
       </c>
       <c r="O6" t="n">
-        <v>3.291771173477173</v>
+        <v>4.433292150497437</v>
       </c>
       <c r="P6" t="n">
-        <v>10.47454977035522</v>
+        <v>2.855153083801269</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.852499008178711</v>
+        <v>3.40892219543457</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-113308</t>
+          <t>20250701-194014</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
